--- a/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=60_without_41.xlsx
+++ b/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=60_without_41.xlsx
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9292414966249675</v>
+        <v>0.9292414966249676</v>
       </c>
       <c r="C3" t="n">
         <v>1.765510165941099</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9564615828171127</v>
+        <v>0.9281574052067807</v>
       </c>
       <c r="C4" t="n">
-        <v>1.896094392796249</v>
+        <v>1.85647958326019</v>
       </c>
       <c r="D4" t="n">
         <v>2.05</v>
@@ -503,7 +503,7 @@
         <v>0.8860063906659643</v>
       </c>
       <c r="C5" t="n">
-        <v>2.116963701972287</v>
+        <v>2.116963701972282</v>
       </c>
       <c r="D5" t="n">
         <v>1.9</v>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9301612847842107</v>
+        <v>0.9301612847842105</v>
       </c>
       <c r="C6" t="n">
         <v>2.032319400203713</v>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.816588760242265</v>
+        <v>0.8165887602422632</v>
       </c>
       <c r="C7" t="n">
         <v>1.598676022617539</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7632215315379387</v>
+        <v>0.9483785159576349</v>
       </c>
       <c r="C8" t="n">
-        <v>2.059771087806624</v>
+        <v>1.947997653348317</v>
       </c>
       <c r="D8" t="n">
         <v>2.52</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9301219891172815</v>
+        <v>0.9301219891172814</v>
       </c>
       <c r="C9" t="n">
-        <v>2.782322965854788</v>
+        <v>2.782322965854785</v>
       </c>
       <c r="D9" t="n">
         <v>2.25</v>
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8487220151491763</v>
+        <v>0.7648303049619503</v>
       </c>
       <c r="C12" t="n">
-        <v>1.411178289905305</v>
+        <v>1.412151378141284</v>
       </c>
       <c r="D12" t="n">
         <v>1.4</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9205200529796191</v>
+        <v>0.9205200529796188</v>
       </c>
       <c r="C13" t="n">
         <v>1.499189239490605</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9193864722484817</v>
+        <v>0.9193864722484825</v>
       </c>
       <c r="C14" t="n">
         <v>1.442971511282391</v>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9511387613105476</v>
+        <v>0.9511387613105475</v>
       </c>
       <c r="C15" t="n">
         <v>1.481508204765064</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8537687361736365</v>
+        <v>0.8537687361736362</v>
       </c>
       <c r="C16" t="n">
         <v>1.338219670154086</v>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7480387660677363</v>
+        <v>0.7480387660677361</v>
       </c>
       <c r="C17" t="n">
-        <v>2.82818752061558</v>
+        <v>2.828187520615586</v>
       </c>
       <c r="D17" t="n">
         <v>2.8</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8117673423584584</v>
+        <v>0.8117673423584586</v>
       </c>
       <c r="C18" t="n">
         <v>2.846217142369086</v>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9119447648315009</v>
+        <v>0.9119447648315011</v>
       </c>
       <c r="C19" t="n">
         <v>1.632012528888971</v>
